--- a/AAII_Financials/Quarterly/VSME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VSME_QTR_FIN.xlsx
@@ -2402,10 +2402,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E41" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F41" s="3">
         <v>7400</v>
@@ -2520,10 +2520,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="E43" s="3">
-        <v>6000</v>
+        <v>6100</v>
       </c>
       <c r="F43" s="3">
         <v>1000</v>
@@ -2638,10 +2638,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
